--- a/InputData/dist-heat/HDL/Heat Distribution Losses.xlsx
+++ b/InputData/dist-heat/HDL/Heat Distribution Losses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\dist-heat\HDL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/dist-heat/HDL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2939486-7725-46EC-BB84-24964CC2395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99579EF0-13B8-0540-AD19-5652900D40F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="2715" windowWidth="19470" windowHeight="20340" xr2:uid="{7FE0438B-EB0E-443A-8B0B-C67805A5FF58}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{7FE0438B-EB0E-443A-8B0B-C67805A5FF58}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -201,8 +201,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -225,9 +224,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -265,7 +264,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -371,7 +370,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -513,7 +512,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -522,18 +521,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FBE8349-D73E-42FD-BD61-5E87CB115BAE}">
   <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="2"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -541,107 +540,107 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>2004</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>2020</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" s="2">
         <v>2016</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2">
         <v>2016</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
@@ -649,7 +648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -657,7 +656,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>5</v>
       </c>
@@ -665,7 +664,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -673,7 +672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -681,22 +680,22 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -718,115 +717,175 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="9">
+      <c r="B1" s="8">
         <v>2020</v>
       </c>
       <c r="C1">
         <v>2021</v>
       </c>
-      <c r="D1" s="9">
+      <c r="D1" s="8">
         <v>2022</v>
       </c>
       <c r="E1">
         <v>2023</v>
       </c>
-      <c r="F1" s="9">
+      <c r="F1" s="8">
         <v>2024</v>
       </c>
       <c r="G1">
         <v>2025</v>
       </c>
-      <c r="H1" s="9">
+      <c r="H1" s="8">
         <v>2026</v>
       </c>
       <c r="I1">
         <v>2027</v>
       </c>
-      <c r="J1" s="9">
+      <c r="J1" s="8">
         <v>2028</v>
       </c>
       <c r="K1">
         <v>2029</v>
       </c>
-      <c r="L1" s="9">
+      <c r="L1" s="8">
         <v>2030</v>
       </c>
       <c r="M1">
         <v>2031</v>
       </c>
-      <c r="N1" s="9">
+      <c r="N1" s="8">
         <v>2032</v>
       </c>
       <c r="O1">
         <v>2033</v>
       </c>
-      <c r="P1" s="9">
+      <c r="P1" s="8">
         <v>2034</v>
       </c>
       <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="R1" s="9">
+      <c r="R1" s="8">
         <v>2036</v>
       </c>
       <c r="S1">
         <v>2037</v>
       </c>
-      <c r="T1" s="9">
+      <c r="T1" s="8">
         <v>2038</v>
       </c>
       <c r="U1">
         <v>2039</v>
       </c>
-      <c r="V1" s="9">
+      <c r="V1" s="8">
         <v>2040</v>
       </c>
       <c r="W1">
         <v>2041</v>
       </c>
-      <c r="X1" s="9">
+      <c r="X1" s="8">
         <v>2042</v>
       </c>
       <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Z1" s="9">
+      <c r="Z1" s="8">
         <v>2044</v>
       </c>
       <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AB1" s="9">
+      <c r="AB1" s="8">
         <v>2046</v>
       </c>
       <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AD1" s="9">
+      <c r="AD1" s="8">
         <v>2048</v>
       </c>
       <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AF1" s="9">
+      <c r="AF1" s="8">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2">
         <f>About!A37</f>
         <v>0.15</v>
       </c>
@@ -948,6 +1007,86 @@
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="AG2">
+        <f>AF2</f>
+        <v>0.15</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ2" si="1">AG2</f>
+        <v>0.15</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="1"/>
         <v>0.15</v>
       </c>
     </row>
